--- a/df_yr1.xlsx
+++ b/df_yr1.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/market_inputs/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_4BB523EAF613C8264F2C4C418D2FEC5E500A85BB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB1FA18A-0DAC-429B-997E-7DB4D37CFD09}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="39">
   <si>
     <t>condition_name</t>
   </si>
@@ -29,6 +23,12 @@
   </si>
   <si>
     <t>subgroup</t>
+  </si>
+  <si>
+    <t>electric_utility</t>
+  </si>
+  <si>
+    <t>gas_utility</t>
   </si>
   <si>
     <t>single_family_year_one</t>
@@ -88,6 +88,15 @@
     <t>whole_home_insultation_efficient_residential</t>
   </si>
   <si>
+    <t>insulation_natural_gas_efficient_residential</t>
+  </si>
+  <si>
+    <t>HERS_electric_efficient_residential</t>
+  </si>
+  <si>
+    <t>HERS_electric_baseline_residential</t>
+  </si>
+  <si>
     <t>heating_cooling</t>
   </si>
   <si>
@@ -117,12 +126,18 @@
   <si>
     <t>none</t>
   </si>
+  <si>
+    <t>test_utility_1</t>
+  </si>
+  <si>
+    <t>test_utility_2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,21 +200,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -237,7 +244,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -271,7 +278,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -306,10 +312,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -482,15 +487,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="35.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J127"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -512,60 +513,78 @@
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2">
-        <v>4000</v>
-      </c>
-      <c r="F2">
-        <v>400</v>
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="H2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+      <c r="I2">
+        <v>5000</v>
+      </c>
+      <c r="J2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3">
+        <v>20000</v>
+      </c>
+      <c r="H3">
+        <v>4000</v>
+      </c>
+      <c r="I3">
         <v>10000</v>
       </c>
-      <c r="F3">
-        <v>2400</v>
-      </c>
-      <c r="G3">
-        <v>5000</v>
-      </c>
-      <c r="H3">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -573,334 +592,3964 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4">
-        <v>10000</v>
-      </c>
-      <c r="F4">
-        <v>1600</v>
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>4000</v>
+        <v>55000</v>
       </c>
       <c r="H4">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3800</v>
+      </c>
+      <c r="I4">
+        <v>9400</v>
+      </c>
+      <c r="J4">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5">
-        <v>21000</v>
-      </c>
-      <c r="F5">
-        <v>4200</v>
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="H5">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+      <c r="I5">
+        <v>5000</v>
+      </c>
+      <c r="J5">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6">
-        <v>9000</v>
-      </c>
-      <c r="F6">
-        <v>600</v>
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
       </c>
       <c r="G6">
-        <v>1500</v>
+        <v>11000</v>
       </c>
       <c r="H6">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+      <c r="I6">
+        <v>5000</v>
+      </c>
+      <c r="J6">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7">
-        <v>49000</v>
-      </c>
-      <c r="F7">
-        <v>16800</v>
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>25000</v>
+        <v>8000</v>
       </c>
       <c r="H7">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+      <c r="I7">
+        <v>5000</v>
+      </c>
+      <c r="J7">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8">
-        <v>21000</v>
-      </c>
-      <c r="F8">
-        <v>4200</v>
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
       </c>
       <c r="G8">
-        <v>7500</v>
+        <v>11000</v>
       </c>
       <c r="H8">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+      <c r="I8">
+        <v>5000</v>
+      </c>
+      <c r="J8">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9">
-        <v>20000</v>
-      </c>
-      <c r="F9">
-        <v>4000</v>
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
       </c>
       <c r="G9">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H9">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+      <c r="I9">
+        <v>2500</v>
+      </c>
+      <c r="J9">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10">
-        <v>25000</v>
-      </c>
-      <c r="F10">
-        <v>6000</v>
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" t="s">
+        <v>38</v>
       </c>
       <c r="G10">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="H10">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2400</v>
+      </c>
+      <c r="I10">
+        <v>5000</v>
+      </c>
+      <c r="J10">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11">
-        <v>25000</v>
-      </c>
-      <c r="F11">
-        <v>6000</v>
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>38</v>
       </c>
       <c r="G11">
-        <v>12500</v>
+        <v>27500</v>
       </c>
       <c r="H11">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2280</v>
+      </c>
+      <c r="I11">
+        <v>4700</v>
+      </c>
+      <c r="J11">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12">
-        <v>25000</v>
-      </c>
-      <c r="F12">
-        <v>6000</v>
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
       </c>
       <c r="G12">
-        <v>12500</v>
+        <v>5000</v>
       </c>
       <c r="H12">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+      <c r="I12">
+        <v>2500</v>
+      </c>
+      <c r="J12">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13">
-        <v>25000</v>
-      </c>
-      <c r="F13">
-        <v>6000</v>
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
       </c>
       <c r="G13">
-        <v>12500</v>
+        <v>5500</v>
       </c>
       <c r="H13">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+      <c r="I13">
+        <v>2500</v>
+      </c>
+      <c r="J13">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
         <v>31</v>
       </c>
-      <c r="E14">
-        <v>50000</v>
-      </c>
-      <c r="F14">
-        <v>10000</v>
+      <c r="E14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
       </c>
       <c r="G14">
-        <v>25000</v>
+        <v>4000</v>
       </c>
       <c r="H14">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+      <c r="I14">
+        <v>2500</v>
+      </c>
+      <c r="J14">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
         <v>31</v>
       </c>
-      <c r="E15">
-        <v>25000</v>
-      </c>
-      <c r="F15">
-        <v>5000</v>
+      <c r="E15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" t="s">
+        <v>38</v>
       </c>
       <c r="G15">
-        <v>12500</v>
+        <v>5500</v>
       </c>
       <c r="H15">
+        <v>600</v>
+      </c>
+      <c r="I15">
         <v>2500</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J15">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
         <v>31</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16">
+        <v>5000</v>
+      </c>
+      <c r="H16">
+        <v>400</v>
+      </c>
+      <c r="I16">
+        <v>2000</v>
+      </c>
+      <c r="J16">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17">
+        <v>10000</v>
+      </c>
+      <c r="H17">
+        <v>1600</v>
+      </c>
+      <c r="I17">
+        <v>4000</v>
+      </c>
+      <c r="J17">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18">
+        <v>27500</v>
+      </c>
+      <c r="H18">
+        <v>1520</v>
+      </c>
+      <c r="I18">
+        <v>3760</v>
+      </c>
+      <c r="J18">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19">
+        <v>5000</v>
+      </c>
+      <c r="H19">
+        <v>400</v>
+      </c>
+      <c r="I19">
+        <v>2000</v>
+      </c>
+      <c r="J19">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20">
+        <v>5500</v>
+      </c>
+      <c r="H20">
+        <v>400</v>
+      </c>
+      <c r="I20">
+        <v>2000</v>
+      </c>
+      <c r="J20">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21">
+        <v>4000</v>
+      </c>
+      <c r="H21">
+        <v>400</v>
+      </c>
+      <c r="I21">
+        <v>2000</v>
+      </c>
+      <c r="J21">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22">
+        <v>5500</v>
+      </c>
+      <c r="H22">
+        <v>400</v>
+      </c>
+      <c r="I22">
+        <v>2000</v>
+      </c>
+      <c r="J22">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23">
+        <v>10500</v>
+      </c>
+      <c r="H23">
+        <v>1050</v>
+      </c>
+      <c r="I23">
+        <v>4500</v>
+      </c>
+      <c r="J23">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24">
+        <v>21000</v>
+      </c>
+      <c r="H24">
+        <v>4200</v>
+      </c>
+      <c r="I24">
+        <v>9000</v>
+      </c>
+      <c r="J24">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25">
+        <v>57749.99999999999</v>
+      </c>
+      <c r="H25">
+        <v>3990</v>
+      </c>
+      <c r="I25">
+        <v>8460</v>
+      </c>
+      <c r="J25">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G26">
+        <v>10500</v>
+      </c>
+      <c r="H26">
+        <v>1050</v>
+      </c>
+      <c r="I26">
+        <v>4500</v>
+      </c>
+      <c r="J26">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27">
+        <v>11550</v>
+      </c>
+      <c r="H27">
+        <v>1050</v>
+      </c>
+      <c r="I27">
+        <v>4500</v>
+      </c>
+      <c r="J27">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" t="s">
+        <v>37</v>
+      </c>
+      <c r="G28">
+        <v>8400</v>
+      </c>
+      <c r="H28">
+        <v>1050</v>
+      </c>
+      <c r="I28">
+        <v>4500</v>
+      </c>
+      <c r="J28">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29">
+        <v>11550</v>
+      </c>
+      <c r="H29">
+        <v>1050</v>
+      </c>
+      <c r="I29">
+        <v>4500</v>
+      </c>
+      <c r="J29">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30">
+        <v>4500</v>
+      </c>
+      <c r="H30">
+        <v>150</v>
+      </c>
+      <c r="I30">
+        <v>750</v>
+      </c>
+      <c r="J30">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31">
+        <v>9000</v>
+      </c>
+      <c r="H31">
+        <v>600</v>
+      </c>
+      <c r="I31">
+        <v>1500</v>
+      </c>
+      <c r="J31">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" t="s">
+        <v>38</v>
+      </c>
+      <c r="G32">
+        <v>24750</v>
+      </c>
+      <c r="H32">
+        <v>570</v>
+      </c>
+      <c r="I32">
+        <v>1410</v>
+      </c>
+      <c r="J32">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" t="s">
+        <v>36</v>
+      </c>
+      <c r="G33">
+        <v>4500</v>
+      </c>
+      <c r="H33">
+        <v>150</v>
+      </c>
+      <c r="I33">
+        <v>750</v>
+      </c>
+      <c r="J33">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" t="s">
+        <v>36</v>
+      </c>
+      <c r="G34">
+        <v>4950</v>
+      </c>
+      <c r="H34">
+        <v>150</v>
+      </c>
+      <c r="I34">
+        <v>750</v>
+      </c>
+      <c r="J34">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" t="s">
+        <v>37</v>
+      </c>
+      <c r="G35">
+        <v>3600</v>
+      </c>
+      <c r="H35">
+        <v>150</v>
+      </c>
+      <c r="I35">
+        <v>750</v>
+      </c>
+      <c r="J35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36">
+        <v>4950</v>
+      </c>
+      <c r="H36">
+        <v>150</v>
+      </c>
+      <c r="I36">
+        <v>750</v>
+      </c>
+      <c r="J36">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E37" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" t="s">
+        <v>37</v>
+      </c>
+      <c r="G37">
+        <v>24500</v>
+      </c>
+      <c r="H37">
+        <v>4200</v>
+      </c>
+      <c r="I37">
+        <v>12500</v>
+      </c>
+      <c r="J37">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" t="s">
+        <v>33</v>
+      </c>
+      <c r="E38" t="s">
+        <v>37</v>
+      </c>
+      <c r="F38" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38">
+        <v>49000</v>
+      </c>
+      <c r="H38">
+        <v>16800</v>
+      </c>
+      <c r="I38">
         <v>25000</v>
       </c>
-      <c r="F16">
+      <c r="J38">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" t="s">
+        <v>33</v>
+      </c>
+      <c r="E39" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39" t="s">
+        <v>38</v>
+      </c>
+      <c r="G39">
+        <v>134750</v>
+      </c>
+      <c r="H39">
+        <v>15960</v>
+      </c>
+      <c r="I39">
+        <v>23500</v>
+      </c>
+      <c r="J39">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" t="s">
+        <v>37</v>
+      </c>
+      <c r="F40" t="s">
+        <v>36</v>
+      </c>
+      <c r="G40">
+        <v>24500</v>
+      </c>
+      <c r="H40">
+        <v>4200</v>
+      </c>
+      <c r="I40">
+        <v>12500</v>
+      </c>
+      <c r="J40">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" t="s">
+        <v>38</v>
+      </c>
+      <c r="F41" t="s">
+        <v>36</v>
+      </c>
+      <c r="G41">
+        <v>26950</v>
+      </c>
+      <c r="H41">
+        <v>4200</v>
+      </c>
+      <c r="I41">
+        <v>12500</v>
+      </c>
+      <c r="J41">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" t="s">
+        <v>33</v>
+      </c>
+      <c r="E42" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" t="s">
+        <v>37</v>
+      </c>
+      <c r="G42">
+        <v>19600</v>
+      </c>
+      <c r="H42">
+        <v>4200</v>
+      </c>
+      <c r="I42">
+        <v>12500</v>
+      </c>
+      <c r="J42">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" t="s">
+        <v>33</v>
+      </c>
+      <c r="E43" t="s">
+        <v>36</v>
+      </c>
+      <c r="F43" t="s">
+        <v>38</v>
+      </c>
+      <c r="G43">
+        <v>26950</v>
+      </c>
+      <c r="H43">
+        <v>4200</v>
+      </c>
+      <c r="I43">
+        <v>12500</v>
+      </c>
+      <c r="J43">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="1">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" t="s">
+        <v>37</v>
+      </c>
+      <c r="F44" t="s">
+        <v>37</v>
+      </c>
+      <c r="G44">
+        <v>10500</v>
+      </c>
+      <c r="H44">
+        <v>1050</v>
+      </c>
+      <c r="I44">
+        <v>3750</v>
+      </c>
+      <c r="J44">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" t="s">
+        <v>37</v>
+      </c>
+      <c r="F45" t="s">
+        <v>38</v>
+      </c>
+      <c r="G45">
+        <v>21000</v>
+      </c>
+      <c r="H45">
+        <v>4200</v>
+      </c>
+      <c r="I45">
+        <v>7500</v>
+      </c>
+      <c r="J45">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" t="s">
+        <v>27</v>
+      </c>
+      <c r="D46" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" t="s">
+        <v>38</v>
+      </c>
+      <c r="F46" t="s">
+        <v>38</v>
+      </c>
+      <c r="G46">
+        <v>57750</v>
+      </c>
+      <c r="H46">
+        <v>3990</v>
+      </c>
+      <c r="I46">
+        <v>7050</v>
+      </c>
+      <c r="J46">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" t="s">
+        <v>37</v>
+      </c>
+      <c r="F47" t="s">
+        <v>36</v>
+      </c>
+      <c r="G47">
+        <v>10500</v>
+      </c>
+      <c r="H47">
+        <v>1050</v>
+      </c>
+      <c r="I47">
+        <v>3750</v>
+      </c>
+      <c r="J47">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" t="s">
+        <v>38</v>
+      </c>
+      <c r="F48" t="s">
+        <v>36</v>
+      </c>
+      <c r="G48">
+        <v>11550</v>
+      </c>
+      <c r="H48">
+        <v>1050</v>
+      </c>
+      <c r="I48">
+        <v>3750</v>
+      </c>
+      <c r="J48">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" t="s">
+        <v>27</v>
+      </c>
+      <c r="D49" t="s">
+        <v>33</v>
+      </c>
+      <c r="E49" t="s">
+        <v>36</v>
+      </c>
+      <c r="F49" t="s">
+        <v>37</v>
+      </c>
+      <c r="G49">
+        <v>8400</v>
+      </c>
+      <c r="H49">
+        <v>1050</v>
+      </c>
+      <c r="I49">
+        <v>3750</v>
+      </c>
+      <c r="J49">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="1">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50" t="s">
+        <v>36</v>
+      </c>
+      <c r="F50" t="s">
+        <v>38</v>
+      </c>
+      <c r="G50">
+        <v>11550</v>
+      </c>
+      <c r="H50">
+        <v>1050</v>
+      </c>
+      <c r="I50">
+        <v>3750</v>
+      </c>
+      <c r="J50">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" t="s">
+        <v>34</v>
+      </c>
+      <c r="E51" t="s">
+        <v>37</v>
+      </c>
+      <c r="F51" t="s">
+        <v>37</v>
+      </c>
+      <c r="G51">
+        <v>10000</v>
+      </c>
+      <c r="H51">
+        <v>1000</v>
+      </c>
+      <c r="I51">
         <v>5000</v>
       </c>
-      <c r="G16">
+      <c r="J51">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" t="s">
+        <v>34</v>
+      </c>
+      <c r="E52" t="s">
+        <v>37</v>
+      </c>
+      <c r="F52" t="s">
+        <v>38</v>
+      </c>
+      <c r="G52">
+        <v>20000</v>
+      </c>
+      <c r="H52">
+        <v>4000</v>
+      </c>
+      <c r="I52">
+        <v>10000</v>
+      </c>
+      <c r="J52">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" t="s">
+        <v>34</v>
+      </c>
+      <c r="E53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F53" t="s">
+        <v>38</v>
+      </c>
+      <c r="G53">
+        <v>55000</v>
+      </c>
+      <c r="H53">
+        <v>3800</v>
+      </c>
+      <c r="I53">
+        <v>9400</v>
+      </c>
+      <c r="J53">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="s">
+        <v>27</v>
+      </c>
+      <c r="D54" t="s">
+        <v>34</v>
+      </c>
+      <c r="E54" t="s">
+        <v>37</v>
+      </c>
+      <c r="F54" t="s">
+        <v>36</v>
+      </c>
+      <c r="G54">
+        <v>10000</v>
+      </c>
+      <c r="H54">
+        <v>1000</v>
+      </c>
+      <c r="I54">
+        <v>5000</v>
+      </c>
+      <c r="J54">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="s">
+        <v>27</v>
+      </c>
+      <c r="D55" t="s">
+        <v>34</v>
+      </c>
+      <c r="E55" t="s">
+        <v>38</v>
+      </c>
+      <c r="F55" t="s">
+        <v>36</v>
+      </c>
+      <c r="G55">
+        <v>11000</v>
+      </c>
+      <c r="H55">
+        <v>1000</v>
+      </c>
+      <c r="I55">
+        <v>5000</v>
+      </c>
+      <c r="J55">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="s">
+        <v>27</v>
+      </c>
+      <c r="D56" t="s">
+        <v>34</v>
+      </c>
+      <c r="E56" t="s">
+        <v>36</v>
+      </c>
+      <c r="F56" t="s">
+        <v>37</v>
+      </c>
+      <c r="G56">
+        <v>8000</v>
+      </c>
+      <c r="H56">
+        <v>1000</v>
+      </c>
+      <c r="I56">
+        <v>5000</v>
+      </c>
+      <c r="J56">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D57" t="s">
+        <v>34</v>
+      </c>
+      <c r="E57" t="s">
+        <v>36</v>
+      </c>
+      <c r="F57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G57">
+        <v>11000</v>
+      </c>
+      <c r="H57">
+        <v>1000</v>
+      </c>
+      <c r="I57">
+        <v>5000</v>
+      </c>
+      <c r="J57">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" t="s">
+        <v>37</v>
+      </c>
+      <c r="F58" t="s">
+        <v>37</v>
+      </c>
+      <c r="G58">
         <v>12500</v>
       </c>
-      <c r="H16">
+      <c r="H58">
+        <v>1500</v>
+      </c>
+      <c r="I58">
+        <v>6250</v>
+      </c>
+      <c r="J58">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" t="s">
+        <v>28</v>
+      </c>
+      <c r="D59" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" t="s">
+        <v>37</v>
+      </c>
+      <c r="F59" t="s">
+        <v>38</v>
+      </c>
+      <c r="G59">
+        <v>25000</v>
+      </c>
+      <c r="H59">
+        <v>6000</v>
+      </c>
+      <c r="I59">
+        <v>12500</v>
+      </c>
+      <c r="J59">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" t="s">
+        <v>28</v>
+      </c>
+      <c r="D60" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" t="s">
+        <v>38</v>
+      </c>
+      <c r="F60" t="s">
+        <v>38</v>
+      </c>
+      <c r="G60">
+        <v>68750</v>
+      </c>
+      <c r="H60">
+        <v>5700</v>
+      </c>
+      <c r="I60">
+        <v>11750</v>
+      </c>
+      <c r="J60">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" t="s">
+        <v>37</v>
+      </c>
+      <c r="F61" t="s">
+        <v>36</v>
+      </c>
+      <c r="G61">
+        <v>12500</v>
+      </c>
+      <c r="H61">
+        <v>1500</v>
+      </c>
+      <c r="I61">
+        <v>6250</v>
+      </c>
+      <c r="J61">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="1">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" t="s">
+        <v>38</v>
+      </c>
+      <c r="F62" t="s">
+        <v>36</v>
+      </c>
+      <c r="G62">
+        <v>13750</v>
+      </c>
+      <c r="H62">
+        <v>1500</v>
+      </c>
+      <c r="I62">
+        <v>6250</v>
+      </c>
+      <c r="J62">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="1">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" t="s">
+        <v>36</v>
+      </c>
+      <c r="F63" t="s">
+        <v>37</v>
+      </c>
+      <c r="G63">
+        <v>10000</v>
+      </c>
+      <c r="H63">
+        <v>1500</v>
+      </c>
+      <c r="I63">
+        <v>6250</v>
+      </c>
+      <c r="J63">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" t="s">
+        <v>36</v>
+      </c>
+      <c r="F64" t="s">
+        <v>38</v>
+      </c>
+      <c r="G64">
+        <v>13750</v>
+      </c>
+      <c r="H64">
+        <v>1500</v>
+      </c>
+      <c r="I64">
+        <v>6250</v>
+      </c>
+      <c r="J64">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" t="s">
+        <v>37</v>
+      </c>
+      <c r="F65" t="s">
+        <v>37</v>
+      </c>
+      <c r="G65">
+        <v>12500</v>
+      </c>
+      <c r="H65">
+        <v>1500</v>
+      </c>
+      <c r="I65">
+        <v>6250</v>
+      </c>
+      <c r="J65">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="1">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" t="s">
+        <v>37</v>
+      </c>
+      <c r="F66" t="s">
+        <v>38</v>
+      </c>
+      <c r="G66">
+        <v>25000</v>
+      </c>
+      <c r="H66">
+        <v>6000</v>
+      </c>
+      <c r="I66">
+        <v>12500</v>
+      </c>
+      <c r="J66">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="1">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" t="s">
+        <v>28</v>
+      </c>
+      <c r="D67" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" t="s">
+        <v>38</v>
+      </c>
+      <c r="F67" t="s">
+        <v>38</v>
+      </c>
+      <c r="G67">
+        <v>68750</v>
+      </c>
+      <c r="H67">
+        <v>5700</v>
+      </c>
+      <c r="I67">
+        <v>11750</v>
+      </c>
+      <c r="J67">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="1">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" t="s">
+        <v>37</v>
+      </c>
+      <c r="F68" t="s">
+        <v>36</v>
+      </c>
+      <c r="G68">
+        <v>12500</v>
+      </c>
+      <c r="H68">
+        <v>1500</v>
+      </c>
+      <c r="I68">
+        <v>6250</v>
+      </c>
+      <c r="J68">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="1">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" t="s">
+        <v>28</v>
+      </c>
+      <c r="D69" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" t="s">
+        <v>38</v>
+      </c>
+      <c r="F69" t="s">
+        <v>36</v>
+      </c>
+      <c r="G69">
+        <v>13750</v>
+      </c>
+      <c r="H69">
+        <v>1500</v>
+      </c>
+      <c r="I69">
+        <v>6250</v>
+      </c>
+      <c r="J69">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="1">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" t="s">
+        <v>28</v>
+      </c>
+      <c r="D70" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" t="s">
+        <v>36</v>
+      </c>
+      <c r="F70" t="s">
+        <v>37</v>
+      </c>
+      <c r="G70">
+        <v>10000</v>
+      </c>
+      <c r="H70">
+        <v>1500</v>
+      </c>
+      <c r="I70">
+        <v>6250</v>
+      </c>
+      <c r="J70">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="1">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" t="s">
+        <v>28</v>
+      </c>
+      <c r="D71" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71" t="s">
+        <v>36</v>
+      </c>
+      <c r="F71" t="s">
+        <v>38</v>
+      </c>
+      <c r="G71">
+        <v>13750</v>
+      </c>
+      <c r="H71">
+        <v>1500</v>
+      </c>
+      <c r="I71">
+        <v>6250</v>
+      </c>
+      <c r="J71">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="1">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" t="s">
+        <v>37</v>
+      </c>
+      <c r="F72" t="s">
+        <v>37</v>
+      </c>
+      <c r="G72">
+        <v>12500</v>
+      </c>
+      <c r="H72">
+        <v>1500</v>
+      </c>
+      <c r="I72">
+        <v>6250</v>
+      </c>
+      <c r="J72">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="1">
+        <v>71</v>
+      </c>
+      <c r="B73" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" t="s">
+        <v>28</v>
+      </c>
+      <c r="D73" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" t="s">
+        <v>37</v>
+      </c>
+      <c r="F73" t="s">
+        <v>38</v>
+      </c>
+      <c r="G73">
+        <v>25000</v>
+      </c>
+      <c r="H73">
+        <v>6000</v>
+      </c>
+      <c r="I73">
+        <v>12500</v>
+      </c>
+      <c r="J73">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="1">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" t="s">
+        <v>38</v>
+      </c>
+      <c r="F74" t="s">
+        <v>38</v>
+      </c>
+      <c r="G74">
+        <v>68750</v>
+      </c>
+      <c r="H74">
+        <v>5700</v>
+      </c>
+      <c r="I74">
+        <v>11750</v>
+      </c>
+      <c r="J74">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="1">
+        <v>73</v>
+      </c>
+      <c r="B75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" t="s">
+        <v>37</v>
+      </c>
+      <c r="F75" t="s">
+        <v>36</v>
+      </c>
+      <c r="G75">
+        <v>12500</v>
+      </c>
+      <c r="H75">
+        <v>1500</v>
+      </c>
+      <c r="I75">
+        <v>6250</v>
+      </c>
+      <c r="J75">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="1">
+        <v>74</v>
+      </c>
+      <c r="B76" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76" t="s">
+        <v>28</v>
+      </c>
+      <c r="D76" t="s">
+        <v>35</v>
+      </c>
+      <c r="E76" t="s">
+        <v>38</v>
+      </c>
+      <c r="F76" t="s">
+        <v>36</v>
+      </c>
+      <c r="G76">
+        <v>13750</v>
+      </c>
+      <c r="H76">
+        <v>1500</v>
+      </c>
+      <c r="I76">
+        <v>6250</v>
+      </c>
+      <c r="J76">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="1">
+        <v>75</v>
+      </c>
+      <c r="B77" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77" t="s">
+        <v>28</v>
+      </c>
+      <c r="D77" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" t="s">
+        <v>36</v>
+      </c>
+      <c r="F77" t="s">
+        <v>37</v>
+      </c>
+      <c r="G77">
+        <v>10000</v>
+      </c>
+      <c r="H77">
+        <v>1500</v>
+      </c>
+      <c r="I77">
+        <v>6250</v>
+      </c>
+      <c r="J77">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="1">
+        <v>76</v>
+      </c>
+      <c r="B78" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" t="s">
+        <v>28</v>
+      </c>
+      <c r="D78" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" t="s">
+        <v>36</v>
+      </c>
+      <c r="F78" t="s">
+        <v>38</v>
+      </c>
+      <c r="G78">
+        <v>13750</v>
+      </c>
+      <c r="H78">
+        <v>1500</v>
+      </c>
+      <c r="I78">
+        <v>6250</v>
+      </c>
+      <c r="J78">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="1">
+        <v>77</v>
+      </c>
+      <c r="B79" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" t="s">
+        <v>28</v>
+      </c>
+      <c r="D79" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" t="s">
+        <v>37</v>
+      </c>
+      <c r="F79" t="s">
+        <v>37</v>
+      </c>
+      <c r="G79">
+        <v>12500</v>
+      </c>
+      <c r="H79">
+        <v>1500</v>
+      </c>
+      <c r="I79">
+        <v>6250</v>
+      </c>
+      <c r="J79">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="1">
+        <v>78</v>
+      </c>
+      <c r="B80" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" t="s">
+        <v>28</v>
+      </c>
+      <c r="D80" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" t="s">
+        <v>37</v>
+      </c>
+      <c r="F80" t="s">
+        <v>38</v>
+      </c>
+      <c r="G80">
+        <v>25000</v>
+      </c>
+      <c r="H80">
+        <v>6000</v>
+      </c>
+      <c r="I80">
+        <v>12500</v>
+      </c>
+      <c r="J80">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" s="1">
+        <v>79</v>
+      </c>
+      <c r="B81" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81" t="s">
+        <v>28</v>
+      </c>
+      <c r="D81" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" t="s">
+        <v>38</v>
+      </c>
+      <c r="F81" t="s">
+        <v>38</v>
+      </c>
+      <c r="G81">
+        <v>68750</v>
+      </c>
+      <c r="H81">
+        <v>5700</v>
+      </c>
+      <c r="I81">
+        <v>11750</v>
+      </c>
+      <c r="J81">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="1">
+        <v>80</v>
+      </c>
+      <c r="B82" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" t="s">
+        <v>37</v>
+      </c>
+      <c r="F82" t="s">
+        <v>36</v>
+      </c>
+      <c r="G82">
+        <v>12500</v>
+      </c>
+      <c r="H82">
+        <v>1500</v>
+      </c>
+      <c r="I82">
+        <v>6250</v>
+      </c>
+      <c r="J82">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="1">
+        <v>81</v>
+      </c>
+      <c r="B83" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F83" t="s">
+        <v>36</v>
+      </c>
+      <c r="G83">
+        <v>13750</v>
+      </c>
+      <c r="H83">
+        <v>1500</v>
+      </c>
+      <c r="I83">
+        <v>6250</v>
+      </c>
+      <c r="J83">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="1">
+        <v>82</v>
+      </c>
+      <c r="B84" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" t="s">
+        <v>28</v>
+      </c>
+      <c r="D84" t="s">
+        <v>35</v>
+      </c>
+      <c r="E84" t="s">
+        <v>36</v>
+      </c>
+      <c r="F84" t="s">
+        <v>37</v>
+      </c>
+      <c r="G84">
+        <v>10000</v>
+      </c>
+      <c r="H84">
+        <v>1500</v>
+      </c>
+      <c r="I84">
+        <v>6250</v>
+      </c>
+      <c r="J84">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="1">
+        <v>83</v>
+      </c>
+      <c r="B85" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85" t="s">
+        <v>28</v>
+      </c>
+      <c r="D85" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" t="s">
+        <v>36</v>
+      </c>
+      <c r="F85" t="s">
+        <v>38</v>
+      </c>
+      <c r="G85">
+        <v>13750</v>
+      </c>
+      <c r="H85">
+        <v>1500</v>
+      </c>
+      <c r="I85">
+        <v>6250</v>
+      </c>
+      <c r="J85">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="1">
+        <v>84</v>
+      </c>
+      <c r="B86" t="s">
+        <v>21</v>
+      </c>
+      <c r="C86" t="s">
+        <v>29</v>
+      </c>
+      <c r="D86" t="s">
+        <v>36</v>
+      </c>
+      <c r="E86" t="s">
+        <v>37</v>
+      </c>
+      <c r="F86" t="s">
+        <v>37</v>
+      </c>
+      <c r="G86">
+        <v>25000</v>
+      </c>
+      <c r="H86">
         <v>2500</v>
+      </c>
+      <c r="I86">
+        <v>12500</v>
+      </c>
+      <c r="J86">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="1">
+        <v>85</v>
+      </c>
+      <c r="B87" t="s">
+        <v>21</v>
+      </c>
+      <c r="C87" t="s">
+        <v>29</v>
+      </c>
+      <c r="D87" t="s">
+        <v>36</v>
+      </c>
+      <c r="E87" t="s">
+        <v>37</v>
+      </c>
+      <c r="F87" t="s">
+        <v>38</v>
+      </c>
+      <c r="G87">
+        <v>50000</v>
+      </c>
+      <c r="H87">
+        <v>10000</v>
+      </c>
+      <c r="I87">
+        <v>25000</v>
+      </c>
+      <c r="J87">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" s="1">
+        <v>86</v>
+      </c>
+      <c r="B88" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" t="s">
+        <v>29</v>
+      </c>
+      <c r="D88" t="s">
+        <v>36</v>
+      </c>
+      <c r="E88" t="s">
+        <v>38</v>
+      </c>
+      <c r="F88" t="s">
+        <v>38</v>
+      </c>
+      <c r="G88">
+        <v>137500</v>
+      </c>
+      <c r="H88">
+        <v>9500</v>
+      </c>
+      <c r="I88">
+        <v>23500</v>
+      </c>
+      <c r="J88">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" s="1">
+        <v>87</v>
+      </c>
+      <c r="B89" t="s">
+        <v>21</v>
+      </c>
+      <c r="C89" t="s">
+        <v>29</v>
+      </c>
+      <c r="D89" t="s">
+        <v>36</v>
+      </c>
+      <c r="E89" t="s">
+        <v>37</v>
+      </c>
+      <c r="F89" t="s">
+        <v>36</v>
+      </c>
+      <c r="G89">
+        <v>25000</v>
+      </c>
+      <c r="H89">
+        <v>2500</v>
+      </c>
+      <c r="I89">
+        <v>12500</v>
+      </c>
+      <c r="J89">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" s="1">
+        <v>88</v>
+      </c>
+      <c r="B90" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90" t="s">
+        <v>29</v>
+      </c>
+      <c r="D90" t="s">
+        <v>36</v>
+      </c>
+      <c r="E90" t="s">
+        <v>38</v>
+      </c>
+      <c r="F90" t="s">
+        <v>36</v>
+      </c>
+      <c r="G90">
+        <v>27500</v>
+      </c>
+      <c r="H90">
+        <v>2500</v>
+      </c>
+      <c r="I90">
+        <v>12500</v>
+      </c>
+      <c r="J90">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" s="1">
+        <v>89</v>
+      </c>
+      <c r="B91" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" t="s">
+        <v>29</v>
+      </c>
+      <c r="D91" t="s">
+        <v>36</v>
+      </c>
+      <c r="E91" t="s">
+        <v>36</v>
+      </c>
+      <c r="F91" t="s">
+        <v>37</v>
+      </c>
+      <c r="G91">
+        <v>20000</v>
+      </c>
+      <c r="H91">
+        <v>2500</v>
+      </c>
+      <c r="I91">
+        <v>12500</v>
+      </c>
+      <c r="J91">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" s="1">
+        <v>90</v>
+      </c>
+      <c r="B92" t="s">
+        <v>21</v>
+      </c>
+      <c r="C92" t="s">
+        <v>29</v>
+      </c>
+      <c r="D92" t="s">
+        <v>36</v>
+      </c>
+      <c r="E92" t="s">
+        <v>36</v>
+      </c>
+      <c r="F92" t="s">
+        <v>38</v>
+      </c>
+      <c r="G92">
+        <v>27500</v>
+      </c>
+      <c r="H92">
+        <v>2500</v>
+      </c>
+      <c r="I92">
+        <v>12500</v>
+      </c>
+      <c r="J92">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" s="1">
+        <v>91</v>
+      </c>
+      <c r="B93" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" t="s">
+        <v>29</v>
+      </c>
+      <c r="D93" t="s">
+        <v>36</v>
+      </c>
+      <c r="E93" t="s">
+        <v>37</v>
+      </c>
+      <c r="F93" t="s">
+        <v>37</v>
+      </c>
+      <c r="G93">
+        <v>12500</v>
+      </c>
+      <c r="H93">
+        <v>1250</v>
+      </c>
+      <c r="I93">
+        <v>6250</v>
+      </c>
+      <c r="J93">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" s="1">
+        <v>92</v>
+      </c>
+      <c r="B94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C94" t="s">
+        <v>29</v>
+      </c>
+      <c r="D94" t="s">
+        <v>36</v>
+      </c>
+      <c r="E94" t="s">
+        <v>37</v>
+      </c>
+      <c r="F94" t="s">
+        <v>38</v>
+      </c>
+      <c r="G94">
+        <v>25000</v>
+      </c>
+      <c r="H94">
+        <v>5000</v>
+      </c>
+      <c r="I94">
+        <v>12500</v>
+      </c>
+      <c r="J94">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" s="1">
+        <v>93</v>
+      </c>
+      <c r="B95" t="s">
+        <v>22</v>
+      </c>
+      <c r="C95" t="s">
+        <v>29</v>
+      </c>
+      <c r="D95" t="s">
+        <v>36</v>
+      </c>
+      <c r="E95" t="s">
+        <v>38</v>
+      </c>
+      <c r="F95" t="s">
+        <v>38</v>
+      </c>
+      <c r="G95">
+        <v>68750</v>
+      </c>
+      <c r="H95">
+        <v>4750</v>
+      </c>
+      <c r="I95">
+        <v>11750</v>
+      </c>
+      <c r="J95">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" s="1">
+        <v>94</v>
+      </c>
+      <c r="B96" t="s">
+        <v>22</v>
+      </c>
+      <c r="C96" t="s">
+        <v>29</v>
+      </c>
+      <c r="D96" t="s">
+        <v>36</v>
+      </c>
+      <c r="E96" t="s">
+        <v>37</v>
+      </c>
+      <c r="F96" t="s">
+        <v>36</v>
+      </c>
+      <c r="G96">
+        <v>12500</v>
+      </c>
+      <c r="H96">
+        <v>1250</v>
+      </c>
+      <c r="I96">
+        <v>6250</v>
+      </c>
+      <c r="J96">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97" s="1">
+        <v>95</v>
+      </c>
+      <c r="B97" t="s">
+        <v>22</v>
+      </c>
+      <c r="C97" t="s">
+        <v>29</v>
+      </c>
+      <c r="D97" t="s">
+        <v>36</v>
+      </c>
+      <c r="E97" t="s">
+        <v>38</v>
+      </c>
+      <c r="F97" t="s">
+        <v>36</v>
+      </c>
+      <c r="G97">
+        <v>13750</v>
+      </c>
+      <c r="H97">
+        <v>1250</v>
+      </c>
+      <c r="I97">
+        <v>6250</v>
+      </c>
+      <c r="J97">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" s="1">
+        <v>96</v>
+      </c>
+      <c r="B98" t="s">
+        <v>22</v>
+      </c>
+      <c r="C98" t="s">
+        <v>29</v>
+      </c>
+      <c r="D98" t="s">
+        <v>36</v>
+      </c>
+      <c r="E98" t="s">
+        <v>36</v>
+      </c>
+      <c r="F98" t="s">
+        <v>37</v>
+      </c>
+      <c r="G98">
+        <v>10000</v>
+      </c>
+      <c r="H98">
+        <v>1250</v>
+      </c>
+      <c r="I98">
+        <v>6250</v>
+      </c>
+      <c r="J98">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" s="1">
+        <v>97</v>
+      </c>
+      <c r="B99" t="s">
+        <v>22</v>
+      </c>
+      <c r="C99" t="s">
+        <v>29</v>
+      </c>
+      <c r="D99" t="s">
+        <v>36</v>
+      </c>
+      <c r="E99" t="s">
+        <v>36</v>
+      </c>
+      <c r="F99" t="s">
+        <v>38</v>
+      </c>
+      <c r="G99">
+        <v>13750</v>
+      </c>
+      <c r="H99">
+        <v>1250</v>
+      </c>
+      <c r="I99">
+        <v>6250</v>
+      </c>
+      <c r="J99">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" s="1">
+        <v>98</v>
+      </c>
+      <c r="B100" t="s">
+        <v>23</v>
+      </c>
+      <c r="C100" t="s">
+        <v>29</v>
+      </c>
+      <c r="D100" t="s">
+        <v>36</v>
+      </c>
+      <c r="E100" t="s">
+        <v>37</v>
+      </c>
+      <c r="F100" t="s">
+        <v>37</v>
+      </c>
+      <c r="G100">
+        <v>10000</v>
+      </c>
+      <c r="H100">
+        <v>1000</v>
+      </c>
+      <c r="I100">
+        <v>5000</v>
+      </c>
+      <c r="J100">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" s="1">
+        <v>99</v>
+      </c>
+      <c r="B101" t="s">
+        <v>23</v>
+      </c>
+      <c r="C101" t="s">
+        <v>29</v>
+      </c>
+      <c r="D101" t="s">
+        <v>36</v>
+      </c>
+      <c r="E101" t="s">
+        <v>37</v>
+      </c>
+      <c r="F101" t="s">
+        <v>38</v>
+      </c>
+      <c r="G101">
+        <v>20000</v>
+      </c>
+      <c r="H101">
+        <v>4000</v>
+      </c>
+      <c r="I101">
+        <v>10000</v>
+      </c>
+      <c r="J101">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" s="1">
+        <v>100</v>
+      </c>
+      <c r="B102" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" t="s">
+        <v>29</v>
+      </c>
+      <c r="D102" t="s">
+        <v>36</v>
+      </c>
+      <c r="E102" t="s">
+        <v>38</v>
+      </c>
+      <c r="F102" t="s">
+        <v>38</v>
+      </c>
+      <c r="G102">
+        <v>55000</v>
+      </c>
+      <c r="H102">
+        <v>3800</v>
+      </c>
+      <c r="I102">
+        <v>9400</v>
+      </c>
+      <c r="J102">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="1">
+        <v>101</v>
+      </c>
+      <c r="B103" t="s">
+        <v>23</v>
+      </c>
+      <c r="C103" t="s">
+        <v>29</v>
+      </c>
+      <c r="D103" t="s">
+        <v>36</v>
+      </c>
+      <c r="E103" t="s">
+        <v>37</v>
+      </c>
+      <c r="F103" t="s">
+        <v>36</v>
+      </c>
+      <c r="G103">
+        <v>10000</v>
+      </c>
+      <c r="H103">
+        <v>1000</v>
+      </c>
+      <c r="I103">
+        <v>5000</v>
+      </c>
+      <c r="J103">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" s="1">
+        <v>102</v>
+      </c>
+      <c r="B104" t="s">
+        <v>23</v>
+      </c>
+      <c r="C104" t="s">
+        <v>29</v>
+      </c>
+      <c r="D104" t="s">
+        <v>36</v>
+      </c>
+      <c r="E104" t="s">
+        <v>38</v>
+      </c>
+      <c r="F104" t="s">
+        <v>36</v>
+      </c>
+      <c r="G104">
+        <v>11000</v>
+      </c>
+      <c r="H104">
+        <v>1000</v>
+      </c>
+      <c r="I104">
+        <v>5000</v>
+      </c>
+      <c r="J104">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" s="1">
+        <v>103</v>
+      </c>
+      <c r="B105" t="s">
+        <v>23</v>
+      </c>
+      <c r="C105" t="s">
+        <v>29</v>
+      </c>
+      <c r="D105" t="s">
+        <v>36</v>
+      </c>
+      <c r="E105" t="s">
+        <v>36</v>
+      </c>
+      <c r="F105" t="s">
+        <v>37</v>
+      </c>
+      <c r="G105">
+        <v>8000</v>
+      </c>
+      <c r="H105">
+        <v>1000</v>
+      </c>
+      <c r="I105">
+        <v>5000</v>
+      </c>
+      <c r="J105">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" s="1">
+        <v>104</v>
+      </c>
+      <c r="B106" t="s">
+        <v>23</v>
+      </c>
+      <c r="C106" t="s">
+        <v>29</v>
+      </c>
+      <c r="D106" t="s">
+        <v>36</v>
+      </c>
+      <c r="E106" t="s">
+        <v>36</v>
+      </c>
+      <c r="F106" t="s">
+        <v>38</v>
+      </c>
+      <c r="G106">
+        <v>11000</v>
+      </c>
+      <c r="H106">
+        <v>1000</v>
+      </c>
+      <c r="I106">
+        <v>5000</v>
+      </c>
+      <c r="J106">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="1">
+        <v>105</v>
+      </c>
+      <c r="B107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" t="s">
+        <v>29</v>
+      </c>
+      <c r="D107" t="s">
+        <v>36</v>
+      </c>
+      <c r="E107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F107" t="s">
+        <v>37</v>
+      </c>
+      <c r="G107">
+        <v>2500</v>
+      </c>
+      <c r="H107">
+        <v>250</v>
+      </c>
+      <c r="I107">
+        <v>1250</v>
+      </c>
+      <c r="J107">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" s="1">
+        <v>106</v>
+      </c>
+      <c r="B108" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" t="s">
+        <v>29</v>
+      </c>
+      <c r="D108" t="s">
+        <v>36</v>
+      </c>
+      <c r="E108" t="s">
+        <v>37</v>
+      </c>
+      <c r="F108" t="s">
+        <v>38</v>
+      </c>
+      <c r="G108">
+        <v>5000</v>
+      </c>
+      <c r="H108">
+        <v>1000</v>
+      </c>
+      <c r="I108">
+        <v>2500</v>
+      </c>
+      <c r="J108">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" s="1">
+        <v>107</v>
+      </c>
+      <c r="B109" t="s">
+        <v>24</v>
+      </c>
+      <c r="C109" t="s">
+        <v>29</v>
+      </c>
+      <c r="D109" t="s">
+        <v>36</v>
+      </c>
+      <c r="E109" t="s">
+        <v>38</v>
+      </c>
+      <c r="F109" t="s">
+        <v>38</v>
+      </c>
+      <c r="G109">
+        <v>13750</v>
+      </c>
+      <c r="H109">
+        <v>950</v>
+      </c>
+      <c r="I109">
+        <v>2350</v>
+      </c>
+      <c r="J109">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" s="1">
+        <v>108</v>
+      </c>
+      <c r="B110" t="s">
+        <v>24</v>
+      </c>
+      <c r="C110" t="s">
+        <v>29</v>
+      </c>
+      <c r="D110" t="s">
+        <v>36</v>
+      </c>
+      <c r="E110" t="s">
+        <v>37</v>
+      </c>
+      <c r="F110" t="s">
+        <v>36</v>
+      </c>
+      <c r="G110">
+        <v>2500</v>
+      </c>
+      <c r="H110">
+        <v>250</v>
+      </c>
+      <c r="I110">
+        <v>1250</v>
+      </c>
+      <c r="J110">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" s="1">
+        <v>109</v>
+      </c>
+      <c r="B111" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" t="s">
+        <v>29</v>
+      </c>
+      <c r="D111" t="s">
+        <v>36</v>
+      </c>
+      <c r="E111" t="s">
+        <v>38</v>
+      </c>
+      <c r="F111" t="s">
+        <v>36</v>
+      </c>
+      <c r="G111">
+        <v>2750</v>
+      </c>
+      <c r="H111">
+        <v>250</v>
+      </c>
+      <c r="I111">
+        <v>1250</v>
+      </c>
+      <c r="J111">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" s="1">
+        <v>110</v>
+      </c>
+      <c r="B112" t="s">
+        <v>24</v>
+      </c>
+      <c r="C112" t="s">
+        <v>29</v>
+      </c>
+      <c r="D112" t="s">
+        <v>36</v>
+      </c>
+      <c r="E112" t="s">
+        <v>36</v>
+      </c>
+      <c r="F112" t="s">
+        <v>37</v>
+      </c>
+      <c r="G112">
+        <v>2000</v>
+      </c>
+      <c r="H112">
+        <v>250</v>
+      </c>
+      <c r="I112">
+        <v>1250</v>
+      </c>
+      <c r="J112">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" s="1">
+        <v>111</v>
+      </c>
+      <c r="B113" t="s">
+        <v>24</v>
+      </c>
+      <c r="C113" t="s">
+        <v>29</v>
+      </c>
+      <c r="D113" t="s">
+        <v>36</v>
+      </c>
+      <c r="E113" t="s">
+        <v>36</v>
+      </c>
+      <c r="F113" t="s">
+        <v>38</v>
+      </c>
+      <c r="G113">
+        <v>2750</v>
+      </c>
+      <c r="H113">
+        <v>250</v>
+      </c>
+      <c r="I113">
+        <v>1250</v>
+      </c>
+      <c r="J113">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" s="1">
+        <v>112</v>
+      </c>
+      <c r="B114" t="s">
+        <v>25</v>
+      </c>
+      <c r="C114" t="s">
+        <v>29</v>
+      </c>
+      <c r="D114" t="s">
+        <v>36</v>
+      </c>
+      <c r="E114" t="s">
+        <v>37</v>
+      </c>
+      <c r="F114" t="s">
+        <v>37</v>
+      </c>
+      <c r="G114">
+        <v>25000</v>
+      </c>
+      <c r="H114">
+        <v>2500</v>
+      </c>
+      <c r="I114">
+        <v>12500</v>
+      </c>
+      <c r="J114">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" s="1">
+        <v>113</v>
+      </c>
+      <c r="B115" t="s">
+        <v>25</v>
+      </c>
+      <c r="C115" t="s">
+        <v>29</v>
+      </c>
+      <c r="D115" t="s">
+        <v>36</v>
+      </c>
+      <c r="E115" t="s">
+        <v>37</v>
+      </c>
+      <c r="F115" t="s">
+        <v>38</v>
+      </c>
+      <c r="G115">
+        <v>50000</v>
+      </c>
+      <c r="H115">
+        <v>10000</v>
+      </c>
+      <c r="I115">
+        <v>25000</v>
+      </c>
+      <c r="J115">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" s="1">
+        <v>114</v>
+      </c>
+      <c r="B116" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116" t="s">
+        <v>29</v>
+      </c>
+      <c r="D116" t="s">
+        <v>36</v>
+      </c>
+      <c r="E116" t="s">
+        <v>38</v>
+      </c>
+      <c r="F116" t="s">
+        <v>38</v>
+      </c>
+      <c r="G116">
+        <v>137500</v>
+      </c>
+      <c r="H116">
+        <v>9500</v>
+      </c>
+      <c r="I116">
+        <v>23500</v>
+      </c>
+      <c r="J116">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" s="1">
+        <v>115</v>
+      </c>
+      <c r="B117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C117" t="s">
+        <v>29</v>
+      </c>
+      <c r="D117" t="s">
+        <v>36</v>
+      </c>
+      <c r="E117" t="s">
+        <v>37</v>
+      </c>
+      <c r="F117" t="s">
+        <v>36</v>
+      </c>
+      <c r="G117">
+        <v>25000</v>
+      </c>
+      <c r="H117">
+        <v>2500</v>
+      </c>
+      <c r="I117">
+        <v>12500</v>
+      </c>
+      <c r="J117">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" s="1">
+        <v>116</v>
+      </c>
+      <c r="B118" t="s">
+        <v>25</v>
+      </c>
+      <c r="C118" t="s">
+        <v>29</v>
+      </c>
+      <c r="D118" t="s">
+        <v>36</v>
+      </c>
+      <c r="E118" t="s">
+        <v>38</v>
+      </c>
+      <c r="F118" t="s">
+        <v>36</v>
+      </c>
+      <c r="G118">
+        <v>27500</v>
+      </c>
+      <c r="H118">
+        <v>2500</v>
+      </c>
+      <c r="I118">
+        <v>12500</v>
+      </c>
+      <c r="J118">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" s="1">
+        <v>117</v>
+      </c>
+      <c r="B119" t="s">
+        <v>25</v>
+      </c>
+      <c r="C119" t="s">
+        <v>29</v>
+      </c>
+      <c r="D119" t="s">
+        <v>36</v>
+      </c>
+      <c r="E119" t="s">
+        <v>36</v>
+      </c>
+      <c r="F119" t="s">
+        <v>37</v>
+      </c>
+      <c r="G119">
+        <v>20000</v>
+      </c>
+      <c r="H119">
+        <v>2500</v>
+      </c>
+      <c r="I119">
+        <v>12500</v>
+      </c>
+      <c r="J119">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120" s="1">
+        <v>118</v>
+      </c>
+      <c r="B120" t="s">
+        <v>25</v>
+      </c>
+      <c r="C120" t="s">
+        <v>29</v>
+      </c>
+      <c r="D120" t="s">
+        <v>36</v>
+      </c>
+      <c r="E120" t="s">
+        <v>36</v>
+      </c>
+      <c r="F120" t="s">
+        <v>38</v>
+      </c>
+      <c r="G120">
+        <v>27500</v>
+      </c>
+      <c r="H120">
+        <v>2500</v>
+      </c>
+      <c r="I120">
+        <v>12500</v>
+      </c>
+      <c r="J120">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="A121" s="1">
+        <v>119</v>
+      </c>
+      <c r="B121" t="s">
+        <v>26</v>
+      </c>
+      <c r="C121" t="s">
+        <v>29</v>
+      </c>
+      <c r="D121" t="s">
+        <v>36</v>
+      </c>
+      <c r="E121" t="s">
+        <v>37</v>
+      </c>
+      <c r="F121" t="s">
+        <v>37</v>
+      </c>
+      <c r="G121">
+        <v>25000</v>
+      </c>
+      <c r="H121">
+        <v>2500</v>
+      </c>
+      <c r="I121">
+        <v>12500</v>
+      </c>
+      <c r="J121">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="A122" s="1">
+        <v>120</v>
+      </c>
+      <c r="B122" t="s">
+        <v>26</v>
+      </c>
+      <c r="C122" t="s">
+        <v>29</v>
+      </c>
+      <c r="D122" t="s">
+        <v>36</v>
+      </c>
+      <c r="E122" t="s">
+        <v>37</v>
+      </c>
+      <c r="F122" t="s">
+        <v>38</v>
+      </c>
+      <c r="G122">
+        <v>50000</v>
+      </c>
+      <c r="H122">
+        <v>10000</v>
+      </c>
+      <c r="I122">
+        <v>25000</v>
+      </c>
+      <c r="J122">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123" s="1">
+        <v>121</v>
+      </c>
+      <c r="B123" t="s">
+        <v>26</v>
+      </c>
+      <c r="C123" t="s">
+        <v>29</v>
+      </c>
+      <c r="D123" t="s">
+        <v>36</v>
+      </c>
+      <c r="E123" t="s">
+        <v>38</v>
+      </c>
+      <c r="F123" t="s">
+        <v>38</v>
+      </c>
+      <c r="G123">
+        <v>137500</v>
+      </c>
+      <c r="H123">
+        <v>9500</v>
+      </c>
+      <c r="I123">
+        <v>23500</v>
+      </c>
+      <c r="J123">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124" s="1">
+        <v>122</v>
+      </c>
+      <c r="B124" t="s">
+        <v>26</v>
+      </c>
+      <c r="C124" t="s">
+        <v>29</v>
+      </c>
+      <c r="D124" t="s">
+        <v>36</v>
+      </c>
+      <c r="E124" t="s">
+        <v>37</v>
+      </c>
+      <c r="F124" t="s">
+        <v>36</v>
+      </c>
+      <c r="G124">
+        <v>25000</v>
+      </c>
+      <c r="H124">
+        <v>2500</v>
+      </c>
+      <c r="I124">
+        <v>12500</v>
+      </c>
+      <c r="J124">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125" s="1">
+        <v>123</v>
+      </c>
+      <c r="B125" t="s">
+        <v>26</v>
+      </c>
+      <c r="C125" t="s">
+        <v>29</v>
+      </c>
+      <c r="D125" t="s">
+        <v>36</v>
+      </c>
+      <c r="E125" t="s">
+        <v>38</v>
+      </c>
+      <c r="F125" t="s">
+        <v>36</v>
+      </c>
+      <c r="G125">
+        <v>27500</v>
+      </c>
+      <c r="H125">
+        <v>2500</v>
+      </c>
+      <c r="I125">
+        <v>12500</v>
+      </c>
+      <c r="J125">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126" s="1">
+        <v>124</v>
+      </c>
+      <c r="B126" t="s">
+        <v>26</v>
+      </c>
+      <c r="C126" t="s">
+        <v>29</v>
+      </c>
+      <c r="D126" t="s">
+        <v>36</v>
+      </c>
+      <c r="E126" t="s">
+        <v>36</v>
+      </c>
+      <c r="F126" t="s">
+        <v>37</v>
+      </c>
+      <c r="G126">
+        <v>20000</v>
+      </c>
+      <c r="H126">
+        <v>2500</v>
+      </c>
+      <c r="I126">
+        <v>12500</v>
+      </c>
+      <c r="J126">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="A127" s="1">
+        <v>125</v>
+      </c>
+      <c r="B127" t="s">
+        <v>26</v>
+      </c>
+      <c r="C127" t="s">
+        <v>29</v>
+      </c>
+      <c r="D127" t="s">
+        <v>36</v>
+      </c>
+      <c r="E127" t="s">
+        <v>36</v>
+      </c>
+      <c r="F127" t="s">
+        <v>38</v>
+      </c>
+      <c r="G127">
+        <v>27500</v>
+      </c>
+      <c r="H127">
+        <v>2500</v>
+      </c>
+      <c r="I127">
+        <v>12500</v>
+      </c>
+      <c r="J127">
+        <v>1250</v>
       </c>
     </row>
   </sheetData>
